--- a/dcf/STNE.xlsx
+++ b/dcf/STNE.xlsx
@@ -843,7 +843,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-08</t>
         </is>
       </c>
     </row>
@@ -1099,25 +1099,25 @@
         </is>
       </c>
       <c r="B4" s="51" t="n">
-        <v>0.04264188022052208</v>
+        <v>0.04183414927117865</v>
       </c>
       <c r="C4" s="51" t="n">
-        <v>0.04764188022052208</v>
+        <v>0.04683414927117865</v>
       </c>
       <c r="D4" s="51" t="n">
-        <v>0.05264188022052208</v>
+        <v>0.05183414927117865</v>
       </c>
       <c r="E4" s="51" t="n">
-        <v>0.05764188022052208</v>
+        <v>0.05683414927117865</v>
       </c>
       <c r="F4" s="51" t="n">
-        <v>0.06264188022052208</v>
+        <v>0.06183414927117865</v>
       </c>
       <c r="G4" s="51" t="n">
-        <v>0.06764188022052207</v>
+        <v>0.06683414927117864</v>
       </c>
       <c r="H4" s="51" t="n">
-        <v>0.07264188022052208</v>
+        <v>0.07183414927117865</v>
       </c>
     </row>
     <row r="5">
@@ -1125,25 +1125,25 @@
         <v>9</v>
       </c>
       <c r="B5" s="8" t="n">
-        <v>66.14413023257816</v>
+        <v>66.56361878324225</v>
       </c>
       <c r="C5" s="8" t="n">
-        <v>63.6201256365821</v>
+        <v>64.01954561635074</v>
       </c>
       <c r="D5" s="8" t="n">
-        <v>61.21645040410372</v>
+        <v>61.59687716818215</v>
       </c>
       <c r="E5" s="8" t="n">
-        <v>58.92667651015456</v>
+        <v>59.28912239934063</v>
       </c>
       <c r="F5" s="8" t="n">
-        <v>56.74475152101505</v>
+        <v>57.09016984998277</v>
       </c>
       <c r="G5" s="8" t="n">
-        <v>54.66497488847993</v>
+        <v>54.99426366362992</v>
       </c>
       <c r="H5" s="8" t="n">
-        <v>52.68197584714916</v>
+        <v>52.9959812335523</v>
       </c>
     </row>
     <row r="6">
@@ -1151,25 +1151,25 @@
         <v>10</v>
       </c>
       <c r="B6" s="8" t="n">
-        <v>70.54097336376934</v>
+        <v>70.994669685571</v>
       </c>
       <c r="C6" s="8" t="n">
-        <v>67.81157392326395</v>
+        <v>68.24344739134249</v>
       </c>
       <c r="D6" s="8" t="n">
-        <v>65.21300893452839</v>
+        <v>65.62423259073894</v>
       </c>
       <c r="E6" s="8" t="n">
-        <v>62.73826695858979</v>
+        <v>63.12994496475108</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>60.38074708621335</v>
+        <v>60.75391908993701</v>
       </c>
       <c r="G6" s="8" t="n">
-        <v>58.13423298923323</v>
+        <v>58.48987819340297</v>
       </c>
       <c r="H6" s="8" t="n">
-        <v>55.99286872849378</v>
+        <v>56.33190968580941</v>
       </c>
     </row>
     <row r="7">
@@ -1177,25 +1177,25 @@
         <v>11</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>74.93781649496053</v>
+        <v>75.42572058789975</v>
       </c>
       <c r="C7" s="8" t="n">
-        <v>72.00302220994584</v>
+        <v>72.46734916633422</v>
       </c>
       <c r="D7" s="8" t="n">
-        <v>69.20956746495307</v>
+        <v>69.65158801329572</v>
       </c>
       <c r="E7" s="8" t="n">
-        <v>66.54985740702503</v>
+        <v>66.97076753016154</v>
       </c>
       <c r="F7" s="8" t="n">
-        <v>64.01674265141163</v>
+        <v>64.41766832989124</v>
       </c>
       <c r="G7" s="8" t="n">
-        <v>61.60349108998653</v>
+        <v>61.98549272317606</v>
       </c>
       <c r="H7" s="8" t="n">
-        <v>59.30376160983839</v>
+        <v>59.66783813806651</v>
       </c>
     </row>
     <row r="8">
@@ -1203,25 +1203,25 @@
         <v>12</v>
       </c>
       <c r="B8" s="8" t="n">
-        <v>79.33465962615172</v>
+        <v>79.8567714902285</v>
       </c>
       <c r="C8" s="8" t="n">
-        <v>76.19447049662772</v>
+        <v>76.69125094132596</v>
       </c>
       <c r="D8" s="8" t="n">
-        <v>73.20612599537776</v>
+        <v>73.6789434358525</v>
       </c>
       <c r="E8" s="53" t="n">
-        <v>70.36144785546027</v>
+        <v>70.81159009557199</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>67.65273821660993</v>
+        <v>68.0814175698455</v>
       </c>
       <c r="G8" s="8" t="n">
-        <v>65.07274919073984</v>
+        <v>65.48110725294913</v>
       </c>
       <c r="H8" s="8" t="n">
-        <v>62.61465449118299</v>
+        <v>63.00376659032364</v>
       </c>
     </row>
     <row r="9">
@@ -1229,25 +1229,25 @@
         <v>13</v>
       </c>
       <c r="B9" s="8" t="n">
-        <v>83.73150275734288</v>
+        <v>84.28782239255723</v>
       </c>
       <c r="C9" s="8" t="n">
-        <v>80.38591878330958</v>
+        <v>80.91515271631771</v>
       </c>
       <c r="D9" s="8" t="n">
-        <v>77.20268452580243</v>
+        <v>77.7062988584093</v>
       </c>
       <c r="E9" s="8" t="n">
-        <v>74.1730383038955</v>
+        <v>74.65241266098243</v>
       </c>
       <c r="F9" s="8" t="n">
-        <v>71.28873378180822</v>
+        <v>71.74516680979974</v>
       </c>
       <c r="G9" s="8" t="n">
-        <v>68.54200729149316</v>
+        <v>68.97672178272219</v>
       </c>
       <c r="H9" s="8" t="n">
-        <v>65.9255473725276</v>
+        <v>66.33969504258074</v>
       </c>
     </row>
     <row r="10">
@@ -1255,25 +1255,25 @@
         <v>14</v>
       </c>
       <c r="B10" s="8" t="n">
-        <v>88.12834588853406</v>
+        <v>88.71887329488598</v>
       </c>
       <c r="C10" s="8" t="n">
-        <v>84.57736706999144</v>
+        <v>85.13905449130944</v>
       </c>
       <c r="D10" s="8" t="n">
-        <v>81.1992430562271</v>
+        <v>81.73365428096609</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>77.98462875233074</v>
+        <v>78.49323522639288</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>74.92472934700652</v>
+        <v>75.40891604975398</v>
       </c>
       <c r="G10" s="8" t="n">
-        <v>72.01126539224644</v>
+        <v>72.47233631249524</v>
       </c>
       <c r="H10" s="8" t="n">
-        <v>69.23644025387222</v>
+        <v>69.67562349483784</v>
       </c>
     </row>
     <row r="11">
@@ -1281,25 +1281,25 @@
         <v>15</v>
       </c>
       <c r="B11" s="8" t="n">
-        <v>92.52518901972525</v>
+        <v>93.14992419721473</v>
       </c>
       <c r="C11" s="8" t="n">
-        <v>88.76881535667333</v>
+        <v>89.36295626630123</v>
       </c>
       <c r="D11" s="8" t="n">
-        <v>85.1958015866518</v>
+        <v>85.76100970352287</v>
       </c>
       <c r="E11" s="8" t="n">
-        <v>81.79621920076598</v>
+        <v>82.33405779180333</v>
       </c>
       <c r="F11" s="8" t="n">
-        <v>78.56072491220482</v>
+        <v>79.07266528970823</v>
       </c>
       <c r="G11" s="8" t="n">
-        <v>75.48052349299977</v>
+        <v>75.96795084226832</v>
       </c>
       <c r="H11" s="8" t="n">
-        <v>72.54733313521682</v>
+        <v>73.01155194709497</v>
       </c>
     </row>
     <row r="13">
@@ -1309,7 +1309,7 @@
         </is>
       </c>
       <c r="B13" s="54" t="n">
-        <v>11.17000007629395</v>
+        <v>10.63500022888184</v>
       </c>
     </row>
     <row r="14">
@@ -1319,7 +1319,7 @@
         </is>
       </c>
       <c r="B14" s="55" t="n">
-        <v>0.05764188022052208</v>
+        <v>0.05683414927117865</v>
       </c>
       <c r="C14" s="56" t="n">
         <v>12</v>
@@ -1665,7 +1665,7 @@
         </is>
       </c>
       <c r="I8" s="48" t="n">
-        <v>0.1606187490370534</v>
+        <v>0.1606734240626314</v>
       </c>
       <c r="K8" s="25">
         <f>MAX(-0.05,NORMINV(RAND(),$C$6,$D$6))</f>
@@ -24404,7 +24404,7 @@
         </is>
       </c>
       <c r="B48" s="23" t="n">
-        <v>11.17000007629395</v>
+        <v>10.63500022888184</v>
       </c>
     </row>
     <row r="49">
@@ -24566,13 +24566,13 @@
         </is>
       </c>
       <c r="B58" s="28" t="n">
-        <v>70.36144785546027</v>
+        <v>70.81159009557199</v>
       </c>
       <c r="C58" s="28" t="n">
-        <v>92.39279558018512</v>
+        <v>93.00158570900703</v>
       </c>
       <c r="D58" s="28" t="n">
-        <v>52.96955518380219</v>
+        <v>53.29564889256406</v>
       </c>
     </row>
     <row r="59">
